--- a/data/processed/positivacao/2025-09_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2025-09_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26531,7 +26531,7 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr"/>
@@ -37805,7 +37805,7 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr"/>
@@ -66073,7 +66073,7 @@
     <row r="2530">
       <c r="A2530" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2530" t="inlineStr"/>
@@ -67692,12 +67692,12 @@
       <c r="A2593" t="inlineStr"/>
       <c r="B2593" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 7 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 2.859,58
+          <t>Vendedor 1 - VENDEDOR 01: positivou 7 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 2.859,58
 Vendedor 18 - LOJA: positivou 267 cliente(s), não positivou 638 cliente(s) - Total vendido: R$ 76.173,07
-Vendedor 3 - FERNANDA: positivou 123 cliente(s), não positivou 310 cliente(s) - Total vendido: R$ 146.784,48
-Vendedor 4 - DANIELA: positivou 123 cliente(s), não positivou 516 cliente(s) - Total vendido: R$ 66.565,47
+Vendedor 3 - VENDEDOR 03: positivou 123 cliente(s), não positivou 310 cliente(s) - Total vendido: R$ 146.784,48
+Vendedor 4 - VENDEDOR 04: positivou 123 cliente(s), não positivou 516 cliente(s) - Total vendido: R$ 66.565,47
 Vendedor 5 - SITE: positivou 2 cliente(s), não positivou 445 cliente(s) - Total vendido: R$ 160,19
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2593" t="inlineStr"/>
